--- a/lesson_11/screening_dashboard.xlsx
+++ b/lesson_11/screening_dashboard.xlsx
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>68000000</v>
+        <v>57650000</v>
       </c>
     </row>
     <row r="12">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>14560000</v>
+        <v>24910000</v>
       </c>
     </row>
   </sheetData>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>обязательство не менее 5 млн руб.; финансовый характер договора; курс относится к более ранней дате</t>
+          <t>обязательство не менее 5 млн руб.; финансовый характер договора</t>
         </is>
       </c>
       <c r="L11" s="7" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>низкий</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>курс относится к более ранней дате</t>
+          <t>повышающие риск факторы не выявлены</t>
         </is>
       </c>
       <c r="L12" s="7" t="n"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>низкий</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>курс относится к более ранней дате</t>
+          <t>повышающие риск факторы не выявлены</t>
         </is>
       </c>
       <c r="L13" s="7" t="n"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>обязательство не менее 5 млн руб.; курс относится к более ранней дате</t>
+          <t>обязательство не менее 5 млн руб.</t>
         </is>
       </c>
       <c r="L15" s="7" t="n"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>низкий</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>курс относится к более ранней дате</t>
+          <t>повышающие риск факторы не выявлены</t>
         </is>
       </c>
       <c r="L16" s="7" t="n"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>низкий</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>курс относится к более ранней дате</t>
+          <t>повышающие риск факторы не выявлены</t>
         </is>
       </c>
       <c r="L17" s="7" t="n"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>обязательство не менее 5 млн руб.; курс относится к более ранней дате</t>
+          <t>обязательство не менее 5 млн руб.</t>
         </is>
       </c>
       <c r="L24" s="7" t="n"/>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>обязательство не менее 5 млн руб.; курс относится к более ранней дате</t>
+          <t>обязательство не менее 5 млн руб.</t>
         </is>
       </c>
       <c r="L30" s="7" t="n"/>
